--- a/PLANILHA MODELO.xlsx
+++ b/PLANILHA MODELO.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>CNPJ</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t xml:space="preserve">Saldo Devedor </t>
+  </si>
+  <si>
+    <t>Processo de Crédito</t>
   </si>
 </sst>
 </file>
@@ -629,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>10</v>
@@ -638,7 +641,7 @@
         <v>15</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
